--- a/Projects/Project 2025/Statement of Applicability and status of information security controls - ISO27k ISMS 6.1 SoA 2022.xlsx
+++ b/Projects/Project 2025/Statement of Applicability and status of information security controls - ISO27k ISMS 6.1 SoA 2022.xlsx
@@ -731,9 +731,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Managed</t>
-  </si>
-  <si>
     <t xml:space="preserve">ISMS scope</t>
   </si>
   <si>
@@ -789,6 +786,9 @@
       </rPr>
       <t xml:space="preserve">according to the standard!</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed</t>
   </si>
   <si>
     <t xml:space="preserve">Leadership</t>
@@ -1047,9 +1047,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Initial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Awareness</t>
   </si>
   <si>
@@ -1081,6 +1078,9 @@
       </rPr>
       <t xml:space="preserve">program</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial</t>
   </si>
   <si>
     <t xml:space="preserve">Communication</t>
@@ -4617,6 +4617,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFD9D9D9"/>
       </font>
       <fill>
@@ -4631,67 +4681,17 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4756,57 +4756,57 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.35"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4851,6 +4851,16 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF336600"/>
         </patternFill>
       </fill>
@@ -4861,67 +4871,57 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFD9D9D9"/>
       </font>
       <fill>
         <patternFill>
           <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4966,32 +4966,42 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD9D9D9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFD9D9D9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -5027,16 +5037,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5077,6 +5077,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFD9D9D9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -5091,67 +5111,47 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.35"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD9D9D9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5192,6 +5192,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFD9D9D9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -5202,26 +5222,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFD9D9D9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -5246,6 +5246,16 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -5257,16 +5267,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5307,6 +5307,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFD9D9D9"/>
       </font>
       <fill>
@@ -5322,56 +5372,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5422,6 +5422,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFD9D9D9"/>
       </font>
       <fill>
@@ -5446,57 +5456,47 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF336600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.35"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5541,77 +5541,77 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD9D9D9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD9D9D9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5656,32 +5656,42 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.35"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFD9D9D9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFD9D9D9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -5717,16 +5727,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF336600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.35"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6785,7 +6785,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.25</c:v>
+                  <c:v>0.214285714285714</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -6794,10 +6794,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.571428571428571</c:v>
+                  <c:v>0.428571428571429</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.178571428571429</c:v>
+                  <c:v>0.357142857142857</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -7247,10 +7247,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.731182795698925</c:v>
+                  <c:v>0.709677419354839</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.193548387096774</c:v>
+                  <c:v>0.21505376344086</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -7321,9 +7321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1465200</xdr:colOff>
+      <xdr:colOff>1464840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55800</xdr:rowOff>
+      <xdr:rowOff>55440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7339,7 +7339,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="218880" y="123840"/>
-          <a:ext cx="1398600" cy="1246320"/>
+          <a:ext cx="1398240" cy="1245960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7365,9 +7365,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>331920</xdr:colOff>
+      <xdr:colOff>331560</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>631080</xdr:rowOff>
+      <xdr:rowOff>630720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7376,7 +7376,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7349400" y="152280"/>
-        <a:ext cx="5797440" cy="5037480"/>
+        <a:ext cx="5797080" cy="5037120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7395,9 +7395,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>303480</xdr:colOff>
+      <xdr:colOff>303120</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7406,7 +7406,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7320960" y="5378040"/>
-        <a:ext cx="5797440" cy="6151680"/>
+        <a:ext cx="5797080" cy="6151320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7423,12 +7423,12 @@
 <c:userShapes xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cdr:relSizeAnchor>
     <cdr:from>
-      <cdr:x>0.105991927972679</cdr:x>
-      <cdr:y>0.0168643704444762</cdr:y>
+      <cdr:x>0.105998509687034</cdr:x>
+      <cdr:y>0.0168655756449653</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.91145606954362</cdr:x>
-      <cdr:y>0.0998999571244819</cdr:y>
+      <cdr:x>0.911326378539493</cdr:x>
+      <cdr:y>0.0998356321017652</cdr:y>
     </cdr:to>
     <cdr:sp>
       <cdr:nvSpPr>
@@ -7438,7 +7438,7 @@
       <cdr:spPr>
         <a:xfrm>
           <a:off x="614520" y="84960"/>
-          <a:ext cx="4669920" cy="418320"/>
+          <a:ext cx="4668840" cy="417960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7487,12 +7487,12 @@
 <c:userShapes xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cdr:relSizeAnchor>
     <cdr:from>
-      <cdr:x>0.105991927972679</cdr:x>
-      <cdr:y>0.0169114635145415</cdr:y>
+      <cdr:x>0.105998509687034</cdr:x>
+      <cdr:y>0.0169124531835206</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.91145606954362</cdr:x>
-      <cdr:y>0.100005851717479</cdr:y>
+      <cdr:x>0.911326378539493</cdr:x>
+      <cdr:y>0.0999531835205993</cdr:y>
     </cdr:to>
     <cdr:sp>
       <cdr:nvSpPr>
@@ -7502,7 +7502,7 @@
       <cdr:spPr>
         <a:xfrm>
           <a:off x="614520" y="104040"/>
-          <a:ext cx="4669920" cy="511200"/>
+          <a:ext cx="4668840" cy="510840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7999,7 +7999,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E8" s="33"/>
     </row>
@@ -8008,7 +8008,7 @@
         <v>4.3</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="27"/>
@@ -8045,10 +8045,10 @@
         <v>4.3</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E10" s="33"/>
     </row>
@@ -8057,7 +8057,7 @@
         <v>4.4</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="27"/>
@@ -8094,10 +8094,10 @@
         <v>4.4</v>
       </c>
       <c r="C12" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>37</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>33</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8156,7 +8156,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8254,7 +8254,7 @@
         <v>44</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E19" s="33"/>
     </row>
@@ -8313,7 +8313,7 @@
         <v>48</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E22" s="33"/>
     </row>
@@ -8325,7 +8325,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E23" s="33"/>
     </row>
@@ -8337,7 +8337,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24" s="33"/>
     </row>
@@ -8386,7 +8386,7 @@
         <v>54</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="28"/>
@@ -8462,7 +8462,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>57</v>
@@ -8550,7 +8550,7 @@
         <v>60</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8599,7 +8599,7 @@
         <v>62</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8608,7 +8608,7 @@
         <v>7.3</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="27"/>
@@ -8645,10 +8645,10 @@
         <v>7.3</v>
       </c>
       <c r="C35" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="32" t="s">
         <v>65</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>63</v>
       </c>
       <c r="E35" s="33"/>
     </row>
@@ -8697,7 +8697,7 @@
         <v>67</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E37" s="33"/>
     </row>
@@ -8746,7 +8746,7 @@
         <v>70</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E39" s="33"/>
     </row>
@@ -8758,7 +8758,7 @@
         <v>72</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E40" s="33"/>
     </row>
@@ -8770,7 +8770,7 @@
         <v>74</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E41" s="33"/>
     </row>
@@ -8856,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E44" s="33"/>
     </row>
@@ -8905,7 +8905,7 @@
         <v>79</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -9013,7 +9013,7 @@
         <v>84</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E51" s="33"/>
     </row>
@@ -9062,7 +9062,7 @@
         <v>86</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E53" s="33"/>
     </row>
@@ -9170,7 +9170,7 @@
         <v>91</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E58" s="33"/>
     </row>
@@ -9219,7 +9219,7 @@
         <v>93</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E60" s="42"/>
     </row>
@@ -9251,7 +9251,7 @@
     <row r="65" customFormat="false" ht="38.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="48" t="n">
         <f aca="false">COUNTIF($D$5:$D$60,"Initial")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B65" s="11"/>
       <c r="D65" s="49"/>
@@ -9275,7 +9275,7 @@
     <row r="68" customFormat="false" ht="38.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="48" t="n">
         <f aca="false">COUNTIF($D$5:$D$60,"managed")</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B68" s="11"/>
       <c r="D68" s="49"/>
@@ -9283,7 +9283,7 @@
     <row r="69" customFormat="false" ht="38.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="48" t="n">
         <f aca="false">COUNTIF($D$5:$D$60,"Optimized")</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B69" s="11"/>
       <c r="D69" s="49"/>
@@ -9600,7 +9600,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{7F79291E-10EB-408D-9193-78D0805C6E87}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{D0AB54F9-BF5B-4190-84E0-C634B0F9DD48}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -9613,7 +9613,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{D8FC982E-5EE0-4075-9E83-52A78A7576AE}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{DEB47C5B-F1FB-4375-9DD0-25F54E73111A}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -9626,7 +9626,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{29DA3813-BF67-49BF-BD36-0086F78366FC}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{186D4CE7-8090-4FFD-A21D-406020331445}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -9639,7 +9639,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{51B77531-C37F-4F9F-83DC-32941B4EC1B2}">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{173DAE6E-E94C-49B1-B738-5F30E0174BD0}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -9652,7 +9652,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{CD494468-104B-48DF-91E4-27EB78528C48}">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{D775A6FD-EC73-4EFB-8250-9C7F441B947C}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -9665,7 +9665,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{9F7E9B12-CBC7-448D-82BF-C7A6FFCAC644}">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{79B9328D-9BD2-4641-B962-63F456488998}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -9678,7 +9678,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{59BC4423-AFFC-4332-AE5C-69D1E0D6D376}">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{845B6136-C0EC-4A73-8BA0-657F99AF3289}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -9691,7 +9691,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{406A2930-D63F-4E38-BD5C-EEA2FE92E34A}">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{D7614792-32FB-4248-8C10-9FF1C5B0CB36}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -9707,7 +9707,7 @@
           <xm:sqref>D60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{8FA9348F-D331-44D9-BFAE-40495375CB27}">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{40AE70E3-DA59-4899-924E-C4F46A8A7F81}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -9720,7 +9720,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{E07AC915-D979-48AB-9160-A3F0B47F94C0}">
+          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{23CD7C7E-29CE-4456-A637-20C0E8513AD0}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -9733,7 +9733,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{BE2F20E2-65FA-48C5-9620-B034C6D9FDA4}">
+          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{E0AF1C9F-9F80-4778-9BC7-BE7ED6C71448}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -9746,7 +9746,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{3E992576-1D40-4728-9BDA-D0DCA4A254D4}">
+          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{79BD4E98-97A9-4249-A840-FB27ADAEC7E5}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -9759,7 +9759,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{E3705F56-3D21-47A0-AE29-8797CAF12E10}">
+          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{B143304A-5CC5-435B-AD65-A08058A0A459}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -9772,7 +9772,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{2CBCE87E-3E3F-4B2F-9B4C-2AD89DA0517B}">
+          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{4433933D-5C60-4742-B792-EF70743BE74D}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -9785,7 +9785,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{6A4C203D-B8BB-43C0-BF53-1AC0402C3A82}">
+          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{6D0060BC-ABD2-47F7-8480-B5C462138A50}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -9798,7 +9798,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{DC1F7E45-F2B2-4480-AACF-FC34C698E344}">
+          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{CB6D64DC-9179-4C37-9AF6-A2E5976BDE1C}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -9814,7 +9814,7 @@
           <xm:sqref>D58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{1E2DF0D2-8E80-4BF2-8357-813872A8EEE1}">
+          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{A0ABBCFA-876A-40E0-878A-8050B34FD1DD}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -9827,7 +9827,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{135E53E9-5F92-4B89-A3AA-F9A298D3EF86}">
+          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{969220B5-9E1B-481E-A72D-388BB48430E0}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -9840,7 +9840,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{399FEF3D-7950-4F7B-93F6-4F641E5A38AE}">
+          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{EBFCC37D-6924-4C50-9AFA-F57DC0F070BA}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -9853,7 +9853,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{B01EAC7F-9C56-483C-B2AE-FB30D4443ABC}">
+          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{545CD582-6E30-41DE-8B56-A7415BC5EEC1}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -9866,7 +9866,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{C58A904A-4E70-424F-8E5D-CA846ED32573}">
+          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{2CFDF8BD-7046-468E-BC84-A4442D57DE7C}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -9879,7 +9879,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{DF30714B-8410-4033-92E8-7B7EC374A948}">
+          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{F233D6F0-2614-4A37-8DFA-F3268B38BB60}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -9892,7 +9892,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{53D500B3-A4E0-4250-A727-86ED3FCFB7E0}">
+          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{33BD2B2D-5954-4EE6-873F-16F01FC585DD}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -9905,7 +9905,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{6AABC56F-F320-4E80-B114-82F95B5B5C6E}">
+          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{7088D745-DDC0-4296-AED5-5681FE2D941F}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -9921,7 +9921,7 @@
           <xm:sqref>D55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{869DB0BD-3A7F-4CC5-AF4C-DA3E645F4257}">
+          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{A5FAF725-8ED0-46B8-A995-9553822437CE}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -9934,7 +9934,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{1F639BB1-E2AC-4F28-805A-EA46B054943B}">
+          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{D52682DE-328C-4241-ADF5-74B04020144E}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -9947,7 +9947,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{3C4D3360-40C9-4D5D-9571-714060CCBF57}">
+          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{2A5F709B-83DD-4583-9D51-48F4767ACB84}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -9960,7 +9960,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{56461888-9EE3-4711-9FEC-3337902CABFB}">
+          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{8043867A-5358-46D4-A7B0-398E4CFD61F2}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -9973,7 +9973,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{C82A8B73-F829-477C-B887-904577183598}">
+          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{8068A5A8-D3C3-44FC-8FF4-F7E0A12FA6FF}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -9986,7 +9986,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{9770CBDC-D960-4512-AA55-12ABC01B366D}">
+          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{DCD2D66F-588C-42F0-B590-EB335FD59F95}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -9999,7 +9999,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{A53840C3-5037-46A7-8A48-38C83BC0E44B}">
+          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{28D53352-339C-4340-A7B1-55734F4D6576}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10012,7 +10012,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{A62BB087-82DB-4347-8131-906072E2D5E1}">
+          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{3080B224-3B82-4FFD-8C8D-186FDB604517}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10028,7 +10028,7 @@
           <xm:sqref>D53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="46" operator="equal" id="{954CB936-FC9A-45E0-97DF-C3D6A66BC217}">
+          <x14:cfRule type="cellIs" priority="46" operator="equal" id="{408B5081-A164-4665-899D-F1F79F409F97}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10041,7 +10041,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="47" operator="equal" id="{003875BA-6B6C-4210-989B-57C7A1E363C7}">
+          <x14:cfRule type="cellIs" priority="47" operator="equal" id="{C3209ADC-CBEC-4847-9E34-50CD1A359589}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10054,7 +10054,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="48" operator="equal" id="{738490C4-9E38-4FCB-B9F2-6994AE8CE880}">
+          <x14:cfRule type="cellIs" priority="48" operator="equal" id="{D6C6778F-E0CE-409E-8AB7-17C1B67B80C1}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10067,7 +10067,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="49" operator="equal" id="{F3A7CF3A-519F-4E50-A168-95C0945E9B7A}">
+          <x14:cfRule type="cellIs" priority="49" operator="equal" id="{B23AEEE7-31C2-48E9-AFE4-78E4124CC5B1}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10080,7 +10080,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="50" operator="equal" id="{51A31649-CAE0-42CD-8B76-8655F360B930}">
+          <x14:cfRule type="cellIs" priority="50" operator="equal" id="{0050F932-1AF6-4C97-81F3-67EF753DB0E8}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10093,7 +10093,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="51" operator="equal" id="{2BD28934-134C-40FC-B53F-4B82606552C0}">
+          <x14:cfRule type="cellIs" priority="51" operator="equal" id="{86594E64-ECED-4250-A8EF-172F29BBE5BE}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10106,7 +10106,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="52" operator="equal" id="{F43F3083-9E61-4A70-BAF8-4A2093805383}">
+          <x14:cfRule type="cellIs" priority="52" operator="equal" id="{384F6B72-59B2-46B8-B073-ED202E7C804E}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10119,7 +10119,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="53" operator="equal" id="{84F21CF0-F478-4738-A3B7-2A9026C39170}">
+          <x14:cfRule type="cellIs" priority="53" operator="equal" id="{432A4300-4A5E-45B9-8AFD-5027C096D0D8}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10135,7 +10135,7 @@
           <xm:sqref>D51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="57" operator="equal" id="{463C8FFF-8A3D-49BD-A546-76DD19CE9B4E}">
+          <x14:cfRule type="cellIs" priority="57" operator="equal" id="{B09C2384-68A0-434F-A5EB-F9994D97ACE7}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10148,7 +10148,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="58" operator="equal" id="{ED16E5B6-7FAA-4CAE-92CB-58DBDCAFB21A}">
+          <x14:cfRule type="cellIs" priority="58" operator="equal" id="{E2A3AF68-5280-4535-B58F-88A04CAD8EA4}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10161,7 +10161,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="59" operator="equal" id="{2131D345-5F76-47B8-A78B-001EB2B4EE65}">
+          <x14:cfRule type="cellIs" priority="59" operator="equal" id="{E13317EC-5820-4B5D-B195-5AC0B6AAB920}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10174,7 +10174,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="60" operator="equal" id="{3480B3AA-9F4D-424C-B66B-77C61D20521B}">
+          <x14:cfRule type="cellIs" priority="60" operator="equal" id="{F3788070-BE89-4370-99E7-A0775F3E128F}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10187,7 +10187,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="61" operator="equal" id="{B764C78B-A86D-461D-AB91-7A97EA668626}">
+          <x14:cfRule type="cellIs" priority="61" operator="equal" id="{82B02FA3-8035-48C4-965C-7DBBD17797CC}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10200,7 +10200,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="62" operator="equal" id="{50B3639C-45E5-4F99-B946-8FAEBEB7E5C5}">
+          <x14:cfRule type="cellIs" priority="62" operator="equal" id="{3FF050E7-9DAA-4D5D-9D8C-E959E99A4D81}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10213,7 +10213,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="63" operator="equal" id="{C69F3370-EAAA-49FA-BD51-1282322016C4}">
+          <x14:cfRule type="cellIs" priority="63" operator="equal" id="{EB4AC9D1-57D9-451B-9085-9F971122D157}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10226,7 +10226,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="64" operator="equal" id="{C14D87D8-AD39-41D3-8950-7516E3528EFF}">
+          <x14:cfRule type="cellIs" priority="64" operator="equal" id="{408FF522-943A-4ADC-8D7B-60665C67D843}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10242,7 +10242,7 @@
           <xm:sqref>D48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="68" operator="equal" id="{ADB22BF4-5B55-49B2-A92E-38F6F4F6E089}">
+          <x14:cfRule type="cellIs" priority="68" operator="equal" id="{4AAD127E-A094-47AF-B034-EC225B963723}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10255,7 +10255,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="69" operator="equal" id="{6BBB1044-B8AE-4341-8550-8D1329456CF0}">
+          <x14:cfRule type="cellIs" priority="69" operator="equal" id="{27A818B8-B5DC-41E5-B0A0-96AE84469352}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10268,7 +10268,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="70" operator="equal" id="{C63D464C-8AE0-4F5B-A194-D65F7DA2BA20}">
+          <x14:cfRule type="cellIs" priority="70" operator="equal" id="{3119B85B-82AB-482A-9650-DA30CCBC4DD3}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10281,7 +10281,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="71" operator="equal" id="{F2A7E54C-3887-4CB4-8812-6DF752E0EEE3}">
+          <x14:cfRule type="cellIs" priority="71" operator="equal" id="{507CCC5A-91F5-4111-A0CE-50C68E4F423B}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10294,7 +10294,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="72" operator="equal" id="{559322A7-5B6D-44F5-9755-40B71567D8C7}">
+          <x14:cfRule type="cellIs" priority="72" operator="equal" id="{D14E5B9A-34C0-4E3C-BE4F-AB6B6A865411}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10307,7 +10307,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="73" operator="equal" id="{00CAEABD-6A68-4DB6-B8D7-E5E7FD1C1E8E}">
+          <x14:cfRule type="cellIs" priority="73" operator="equal" id="{E56965F4-F443-428A-B16C-59B0F4757814}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10320,7 +10320,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="74" operator="equal" id="{38121B3A-DA57-4EFE-B4C5-00DEA2CB68C1}">
+          <x14:cfRule type="cellIs" priority="74" operator="equal" id="{455C8F2F-66B6-486A-AD6A-34C250B77D99}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10333,7 +10333,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="75" operator="equal" id="{2750144A-51EC-4588-A8F5-D0D38DDAF578}">
+          <x14:cfRule type="cellIs" priority="75" operator="equal" id="{00F2FA7F-BFDD-48C2-B328-19A5EF336BED}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10349,7 +10349,7 @@
           <xm:sqref>D46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="79" operator="equal" id="{5EFD6DC8-1EDD-4494-91B5-B3ED30235636}">
+          <x14:cfRule type="cellIs" priority="79" operator="equal" id="{A42F35F9-5D46-44D8-A9BE-CF74F05375C6}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10362,7 +10362,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="80" operator="equal" id="{D6244B1C-E080-4678-90A7-2718F732786D}">
+          <x14:cfRule type="cellIs" priority="80" operator="equal" id="{56A3BB35-75B1-4CF0-A420-8A57EDFEEC94}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10375,7 +10375,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="81" operator="equal" id="{37BF11BF-8F91-4D2D-9467-9A14142D2F3B}">
+          <x14:cfRule type="cellIs" priority="81" operator="equal" id="{F992FFA0-FC74-47A4-BE11-AC2CCE9EE316}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10388,7 +10388,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="82" operator="equal" id="{913ACCA4-4CC2-47DB-A352-BF846F48BFE4}">
+          <x14:cfRule type="cellIs" priority="82" operator="equal" id="{2E71B060-6430-41EC-AFB9-D7E864F7B45C}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10401,7 +10401,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="83" operator="equal" id="{15836610-F483-4588-ADF7-E8AB444993A1}">
+          <x14:cfRule type="cellIs" priority="83" operator="equal" id="{58E786DA-2950-44C1-90CC-67C473B5A93E}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10414,7 +10414,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="84" operator="equal" id="{3A687366-4C49-4760-A690-9B1986E6AEAB}">
+          <x14:cfRule type="cellIs" priority="84" operator="equal" id="{2E27D0F3-138C-4E4A-B3E2-369327C52079}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10427,7 +10427,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="85" operator="equal" id="{4C9DD1DD-7057-4880-BB63-E04287E1F336}">
+          <x14:cfRule type="cellIs" priority="85" operator="equal" id="{7ACF5BC8-8184-4AD9-8F8F-50FDC0F05CB7}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10440,7 +10440,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="86" operator="equal" id="{4291F58B-BA4A-4042-AC42-81F176C0B493}">
+          <x14:cfRule type="cellIs" priority="86" operator="equal" id="{E0A83000-DA35-41F9-B9D3-4DF9D36DE346}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10456,7 +10456,7 @@
           <xm:sqref>D44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="90" operator="equal" id="{603E227B-E089-45D0-BCEC-F0FF9562B579}">
+          <x14:cfRule type="cellIs" priority="90" operator="equal" id="{C2538170-AAA6-448B-8BF0-10BCC7A03C1C}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10469,7 +10469,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="91" operator="equal" id="{94BAB8B4-7C73-42FC-B71F-C1DDDA2B349C}">
+          <x14:cfRule type="cellIs" priority="91" operator="equal" id="{54604426-CB60-423D-965C-DA9AD5E2EF6F}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10482,7 +10482,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="92" operator="equal" id="{6ACA54EA-9059-4D9C-A6FC-DA627D377EAE}">
+          <x14:cfRule type="cellIs" priority="92" operator="equal" id="{2C5BA881-6841-4537-B545-33EF3B00357B}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10495,7 +10495,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="93" operator="equal" id="{90A57E59-F9B6-4313-8093-4CDEAD6E8253}">
+          <x14:cfRule type="cellIs" priority="93" operator="equal" id="{725C9050-B1BE-4F10-9A32-369991F4AC2C}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10508,7 +10508,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="94" operator="equal" id="{EC99778C-8120-489A-833A-1048A65B3B17}">
+          <x14:cfRule type="cellIs" priority="94" operator="equal" id="{3CA6EB5F-9061-437C-A7D9-C029C6541D60}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10521,7 +10521,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="95" operator="equal" id="{8E6600DB-3653-4A63-AAD4-339A99E7B8B6}">
+          <x14:cfRule type="cellIs" priority="95" operator="equal" id="{204F50A0-6AFE-463C-8A76-B7224E485A80}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10534,7 +10534,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="96" operator="equal" id="{D988FEBF-EFEE-4CB0-9C98-BDF580E89014}">
+          <x14:cfRule type="cellIs" priority="96" operator="equal" id="{1949E018-89ED-4530-B840-914FE02A3290}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10547,7 +10547,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="97" operator="equal" id="{9F99D0F3-284F-4F5E-BFF6-86603EF13836}">
+          <x14:cfRule type="cellIs" priority="97" operator="equal" id="{18B57771-F6E8-4CA2-A3C9-EE3997EB4A92}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10563,7 +10563,7 @@
           <xm:sqref>D39:D41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="101" operator="equal" id="{262978B0-26A9-4399-848F-13DED93659E8}">
+          <x14:cfRule type="cellIs" priority="101" operator="equal" id="{96ACA060-AFD0-4585-BD11-74EF35A1C51D}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10576,7 +10576,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="102" operator="equal" id="{32498498-CF23-45C0-AD90-793D1477896D}">
+          <x14:cfRule type="cellIs" priority="102" operator="equal" id="{586024E9-ABD5-41D0-A578-2E8A38346057}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10589,7 +10589,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="103" operator="equal" id="{9470FC6A-44A7-45D0-BB28-442E61D2D09E}">
+          <x14:cfRule type="cellIs" priority="103" operator="equal" id="{55834EFA-C435-45FF-BEB0-AE14378D17B8}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10602,7 +10602,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="104" operator="equal" id="{1388368F-8711-42CC-8F16-9BC1436A803C}">
+          <x14:cfRule type="cellIs" priority="104" operator="equal" id="{27D5E731-843C-4A18-AD7F-00F728ABFCCA}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10615,7 +10615,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="105" operator="equal" id="{4047F7E6-7FC7-4F75-AFFD-3839415CB9F4}">
+          <x14:cfRule type="cellIs" priority="105" operator="equal" id="{2C4E6E34-1973-42E3-90F0-1BFA2CB193B5}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10628,7 +10628,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="106" operator="equal" id="{92E4EF4F-5819-4A3C-9D5F-2C9737993AAD}">
+          <x14:cfRule type="cellIs" priority="106" operator="equal" id="{7C2051DE-231F-4EAF-B8B2-2D44EFEF99E3}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10641,7 +10641,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="107" operator="equal" id="{EE71A7EF-EA1D-4DFA-A24F-BBA27564D5A0}">
+          <x14:cfRule type="cellIs" priority="107" operator="equal" id="{CD9A33BD-6BF8-4B80-BA79-E030C1F173CA}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10654,7 +10654,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="108" operator="equal" id="{727DF6DD-A78E-4E69-A1ED-E617E421A9A3}">
+          <x14:cfRule type="cellIs" priority="108" operator="equal" id="{F3CCDCBC-BCC6-414F-9D9E-6A5C4E36F45B}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10670,7 +10670,7 @@
           <xm:sqref>D37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="112" operator="equal" id="{98B52B30-D37F-487F-BAA4-B7605685F7D9}">
+          <x14:cfRule type="cellIs" priority="112" operator="equal" id="{BA47FF41-3B98-47ED-9E12-E1508D38A224}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10683,7 +10683,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="113" operator="equal" id="{F3D0454B-60A2-4CD9-B722-C47624FA5C2D}">
+          <x14:cfRule type="cellIs" priority="113" operator="equal" id="{F06C3C76-8C8B-44EA-BB4E-F98324BD11C8}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10696,7 +10696,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="114" operator="equal" id="{7380DEC0-EB4B-40F0-B69D-81CA88A82270}">
+          <x14:cfRule type="cellIs" priority="114" operator="equal" id="{1DD3D892-FADA-4D27-AE38-3ADA3286E1B1}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10709,7 +10709,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="115" operator="equal" id="{55FF65D1-F397-493A-BBD2-46125BD3E395}">
+          <x14:cfRule type="cellIs" priority="115" operator="equal" id="{8F42DF51-6016-4B8F-89D7-992CB54E74F0}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10722,7 +10722,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="116" operator="equal" id="{16A781AF-57A3-447B-A932-254B23441733}">
+          <x14:cfRule type="cellIs" priority="116" operator="equal" id="{B45D37F9-396D-4264-9E48-64C3C71D49AC}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10735,7 +10735,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="117" operator="equal" id="{B8D729EC-7BA2-4FAB-AA8D-1A52CF9DE25E}">
+          <x14:cfRule type="cellIs" priority="117" operator="equal" id="{1A8A8C75-AB50-43F9-9C46-EC71DAE64000}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10748,7 +10748,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="118" operator="equal" id="{6FF051AE-87A7-4D42-A559-A4DFDD15F047}">
+          <x14:cfRule type="cellIs" priority="118" operator="equal" id="{E31DBEED-30BF-4C78-8CA0-9219A049B718}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10761,7 +10761,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="119" operator="equal" id="{3CA8F8F9-9D28-4C2F-A036-2C305089CB6B}">
+          <x14:cfRule type="cellIs" priority="119" operator="equal" id="{FA884B64-EF90-4FAB-AA2A-52DE8040E95E}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10777,7 +10777,7 @@
           <xm:sqref>D35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="123" operator="equal" id="{DE4036DE-7098-494D-8956-E82CAD6E589A}">
+          <x14:cfRule type="cellIs" priority="123" operator="equal" id="{4D1687EF-6A9B-4275-9712-BFEF50B4DB8F}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10790,7 +10790,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="124" operator="equal" id="{29D4E119-8C32-4D50-9F6D-2C29BA8FD7C1}">
+          <x14:cfRule type="cellIs" priority="124" operator="equal" id="{E6500016-6E33-4F3E-B7E9-B2702089C655}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10803,7 +10803,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="125" operator="equal" id="{D15BEC5D-C633-415F-819F-969F40BD6AAB}">
+          <x14:cfRule type="cellIs" priority="125" operator="equal" id="{5B54A05B-15FA-4D52-92EB-463CC168B9B6}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10816,7 +10816,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="126" operator="equal" id="{FEE1A0CC-E15C-4A5E-AA6A-F6115ABE78D2}">
+          <x14:cfRule type="cellIs" priority="126" operator="equal" id="{EDC1B318-2A77-45B0-A1AA-93D2ACA9B991}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10829,7 +10829,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="127" operator="equal" id="{C3B559B2-BE00-41AE-9320-35A6A42D19F7}">
+          <x14:cfRule type="cellIs" priority="127" operator="equal" id="{39A8A6AB-E1AC-49B0-AD55-4AAD007CF1C2}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10842,7 +10842,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="128" operator="equal" id="{19D7196E-F2CB-4CF1-ADB7-8B7F87C7CBD1}">
+          <x14:cfRule type="cellIs" priority="128" operator="equal" id="{30103AA7-C95F-4560-B0EC-1088864C6152}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10855,7 +10855,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="129" operator="equal" id="{156873C4-9563-40FC-8AC8-3CBA9F6ADEB2}">
+          <x14:cfRule type="cellIs" priority="129" operator="equal" id="{A77855B5-59B1-4A27-8E3C-5BFDDFE88FA7}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10868,7 +10868,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="130" operator="equal" id="{7D68C5C9-C027-4951-AD5E-F5588364A371}">
+          <x14:cfRule type="cellIs" priority="130" operator="equal" id="{E6E08621-249D-4D7B-8757-8ED745B8AFB5}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10884,7 +10884,7 @@
           <xm:sqref>D33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="134" operator="equal" id="{90D16AAD-C59E-4C30-9A5C-F9B65072352D}">
+          <x14:cfRule type="cellIs" priority="134" operator="equal" id="{2B161CFE-B71A-4924-AEE0-8C605C26A5F7}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -10897,7 +10897,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="135" operator="equal" id="{DA26FB60-F31E-409B-893A-46355E918FF9}">
+          <x14:cfRule type="cellIs" priority="135" operator="equal" id="{F7AB3990-42F5-4662-9E9F-20EB404DD071}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -10910,7 +10910,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="136" operator="equal" id="{6AE3D8D3-CB3B-4E1A-8240-DBD6F9E7FE40}">
+          <x14:cfRule type="cellIs" priority="136" operator="equal" id="{E7B6BBB8-59D1-40B4-8C3A-C0742CE8D640}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -10923,7 +10923,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="137" operator="equal" id="{15D2DB19-3EC6-41BF-8FCC-B6499FDA59D0}">
+          <x14:cfRule type="cellIs" priority="137" operator="equal" id="{6D847C38-2382-45DB-9222-CEDA93CE60B4}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -10936,7 +10936,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="138" operator="equal" id="{EBF04590-9420-45D6-8196-B8D127819B68}">
+          <x14:cfRule type="cellIs" priority="138" operator="equal" id="{B8597935-722E-4C1E-8553-EAD0B2B3174A}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -10949,7 +10949,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="139" operator="equal" id="{52E23192-54BA-44A6-B961-ABF3B1D476EE}">
+          <x14:cfRule type="cellIs" priority="139" operator="equal" id="{A0E76120-8384-425F-B7DD-C61DF1204FF9}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -10962,7 +10962,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="140" operator="equal" id="{31E74743-EC95-428E-8077-4BC5649735D2}">
+          <x14:cfRule type="cellIs" priority="140" operator="equal" id="{E6693088-1A91-4DA0-81F8-FEF89F418FC8}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -10975,7 +10975,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="141" operator="equal" id="{6E6021EA-361B-4014-9F86-1B25D56C3F27}">
+          <x14:cfRule type="cellIs" priority="141" operator="equal" id="{6693BAA9-F841-43A4-A483-C639163A53C4}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -10991,10 +10991,75 @@
           <xm:sqref>D31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="145" operator="equal" id="{13801EA2-20FC-4977-A278-B479A399687F}">
+          <x14:cfRule type="cellIs" priority="145" operator="equal" id="{9D598D6E-1064-45E8-B850-9E26117514DC}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="146" operator="equal" id="{6AB1F253-10EC-4495-94CE-B0A61CED88D8}">
+            <xm:f>Metrics!$B$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="147" operator="equal" id="{21BB119C-A028-4D29-9652-D9F495693BE6}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="148" operator="equal" id="{F1E15719-80F7-4FC6-84FB-81FA9D8B1220}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="149" operator="equal" id="{B69FE922-A0CD-4A7C-90FE-755C27E48C60}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="150" operator="equal" id="{127667E0-369F-4841-9E85-5ED884A037A0}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
                 <color rgb="FFD9D9D9"/>
               </font>
               <fill>
@@ -11004,8 +11069,21 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="146" operator="equal" id="{6048A2D3-EEC9-45C4-A5D7-7298356527F0}">
-            <xm:f>Metrics!$B$3</xm:f>
+          <x14:cfRule type="cellIs" priority="151" operator="equal" id="{962F5851-7225-4C5C-952D-F259322E9BFB}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="152" operator="equal" id="{24E778F0-7020-4DF1-B54B-D54F86E294E8}">
+            <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11013,84 +11091,6 @@
               <fill>
                 <patternFill>
                   <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="147" operator="equal" id="{70E2AADF-9873-4031-A8A5-87D6AD486381}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="148" operator="equal" id="{8A18C1AD-C453-487B-BB7B-1FF45052B117}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="149" operator="equal" id="{3DF6D97D-92FB-4EA6-80FA-272FEFCE489D}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="150" operator="equal" id="{A3C98059-73D9-47AC-B384-4C9980A28927}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="151" operator="equal" id="{00EA2D61-72BF-4990-90BD-79C498D356CD}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="152" operator="equal" id="{40B9D817-D31F-4C86-9235-A68D4BA78D27}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11098,7 +11098,7 @@
           <xm:sqref>D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="156" operator="equal" id="{80752D63-33C8-48B0-8749-8E5CB71ECAF9}">
+          <x14:cfRule type="cellIs" priority="156" operator="equal" id="{999681CD-AA41-41B8-916E-BBE6E6B7165D}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -11111,7 +11111,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="157" operator="equal" id="{7980FA3D-8777-4A70-8C20-EC41F1BC202C}">
+          <x14:cfRule type="cellIs" priority="157" operator="equal" id="{12DC1A6C-60F0-4C99-BF95-142D9FEC8D3A}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -11124,7 +11124,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="158" operator="equal" id="{F4821FDA-1E28-4BEA-9A65-9A268089C694}">
+          <x14:cfRule type="cellIs" priority="158" operator="equal" id="{90A95530-A326-48C7-A176-4A7570D9C214}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -11132,72 +11132,72 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="159" operator="equal" id="{66DBEBE0-23A7-44EC-BB21-DE7DCF42E596}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="160" operator="equal" id="{D34DC050-66EC-497F-8116-58ED27E1A3CC}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="161" operator="equal" id="{3E8A2FEF-6CDD-40A0-ABF8-B142FDCB70C0}">
+            <xm:f>Metrics!$B$10</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="162" operator="equal" id="{8134D9E6-E915-455C-9FC3-2969145B11D1}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="163" operator="equal" id="{BBACA06E-7DF3-4845-88EC-96A27DF5366D}">
+            <xm:f>Metrics!$B$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="159" operator="equal" id="{4050B619-834D-4194-8882-77E0A48DA7AA}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="160" operator="equal" id="{15A1C297-4547-49E9-99C8-2FDC40E26050}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="161" operator="equal" id="{179E399E-D03C-458B-93E8-FD70C4B250B2}">
-            <xm:f>Metrics!$B$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="162" operator="equal" id="{68782BD8-8D73-4B6A-A78D-1426FA8A77B0}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="163" operator="equal" id="{CC20E143-40E5-48A9-989E-359FAFECDAAD}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11205,7 +11205,7 @@
           <xm:sqref>D26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="167" operator="equal" id="{F76EC037-F822-40E3-AB90-A5D6CD5DD020}">
+          <x14:cfRule type="cellIs" priority="167" operator="equal" id="{77FC41BD-62CA-4BBA-8766-DC49B597E63E}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -11213,13 +11213,78 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="168" operator="equal" id="{528F86A5-1B81-49AF-A579-6A70547EAC6A}">
+            <xm:f>Metrics!$B$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor rgb="FF336600"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="168" operator="equal" id="{3C319017-6076-4D80-9620-1F29F96FF880}">
-            <xm:f>Metrics!$B$3</xm:f>
+          <x14:cfRule type="cellIs" priority="169" operator="equal" id="{EF4D1C17-F874-4F3A-A3D0-2072CF6E2D2D}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="170" operator="equal" id="{476E3E9A-D954-4DA3-AC8C-6B80A396BE50}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="171" operator="equal" id="{F57565A4-121F-4029-9B2D-C682BEE7A89C}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="172" operator="equal" id="{9BE56860-2974-422E-BF9C-473EF97EE482}">
+            <xm:f>Metrics!$B$10</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="173" operator="equal" id="{2071D0E8-F060-4D60-8696-E14420A01763}">
+            <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11231,47 +11296,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="169" operator="equal" id="{3DE71831-F13B-4CB6-89A0-6613F0D7E3C0}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="170" operator="equal" id="{B2404C2A-5BE9-44FC-9ABE-6C3DCC34DBEF}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="171" operator="equal" id="{1DE46966-8422-404D-8066-77625FC7B624}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="172" operator="equal" id="{6569CA46-CB9F-4FA4-8312-A646AD2C7F5C}">
-            <xm:f>Metrics!$B$10</xm:f>
+          <x14:cfRule type="cellIs" priority="174" operator="equal" id="{E550DAD6-5F7A-4776-9794-742E40543DB8}">
+            <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFD9D9D9"/>
@@ -11279,32 +11305,6 @@
               <fill>
                 <patternFill>
                   <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="173" operator="equal" id="{78CCBF8B-2F29-4CF8-91B2-2EF8E1F61F8E}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="174" operator="equal" id="{D74CC9E5-41A6-42BC-95DB-203BEC4EEFE1}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11312,7 +11312,7 @@
           <xm:sqref>D22:D24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="178" operator="equal" id="{54AC79DB-7E9E-4960-8A19-8F89172E82B5}">
+          <x14:cfRule type="cellIs" priority="178" operator="equal" id="{A859EB69-60A0-43D8-B79B-6CB3A1A5B7A9}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -11320,39 +11320,52 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="179" operator="equal" id="{1BC0C9D1-66F9-469E-9928-C13FCC26E78C}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFD9D9D9"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="180" operator="equal" id="{682EDD33-83F0-4AC0-B5F7-99F0997EE7CD}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="181" operator="equal" id="{C2DC555C-47BE-44E9-AC46-A9B6BAF05BEB}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor rgb="FFC00000"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="179" operator="equal" id="{B6F179F5-C054-4FD6-BAC9-72DEB0E65CBF}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFD9D9D9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="180" operator="equal" id="{8DC2FB00-8C36-4CC4-83D7-D6DDC7D92190}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="181" operator="equal" id="{9E775071-F0BC-4C3A-912C-CCA5776353AB}">
-            <xm:f>Metrics!$B$6</xm:f>
+          <x14:cfRule type="cellIs" priority="182" operator="equal" id="{D9932DB8-BD61-427A-98E8-C6AB7AADC4CB}">
+            <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11364,8 +11377,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="182" operator="equal" id="{E32D3CC7-F8EB-4B10-B4A1-62457944EABF}">
-            <xm:f>Metrics!$B$7</xm:f>
+          <x14:cfRule type="cellIs" priority="183" operator="equal" id="{41D2B44C-CD4A-455E-BDBB-AFDE37CF8591}">
+            <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11377,8 +11390,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="183" operator="equal" id="{B4E08330-D6F3-4B81-8185-66D8798D59D0}">
-            <xm:f>Metrics!$B$8</xm:f>
+          <x14:cfRule type="cellIs" priority="184" operator="equal" id="{F145CB1B-4C78-432E-92BD-3E86DC4550C1}">
+            <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11390,8 +11403,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="184" operator="equal" id="{AFB6C6E0-8C44-486E-83A2-F01DF1BA89A1}">
-            <xm:f>Metrics!$B$9</xm:f>
+          <x14:cfRule type="cellIs" priority="185" operator="equal" id="{8ED29F77-B8A1-4C8B-A487-AC60C7DBFD73}">
+            <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11399,19 +11412,6 @@
               <fill>
                 <patternFill>
                   <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="185" operator="equal" id="{7AF71DDD-90B0-4727-94C6-DBF0924D82C3}">
-            <xm:f>Metrics!$B$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11419,10 +11419,36 @@
           <xm:sqref>D5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="189" operator="equal" id="{FD2AAFF3-9872-4ADD-815D-1EB1BEDD5EBF}">
+          <x14:cfRule type="cellIs" priority="189" operator="equal" id="{C1F428E5-AF8C-49B0-A724-E3E74B385075}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
+                <color rgb="FFD9D9D9"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="190" operator="equal" id="{9E7833DA-E1D0-4434-BBB4-6FD6EA50D85D}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="191" operator="equal" id="{16796AC2-2436-4689-AAA1-AC557A48C2DF}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
                 <color rgb="FFFFFFFF"/>
               </font>
               <fill>
@@ -11432,8 +11458,60 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="190" operator="equal" id="{CC6EA8D0-90C9-49E4-9679-62DEE749338B}">
-            <xm:f>Metrics!$B$4</xm:f>
+          <x14:cfRule type="cellIs" priority="192" operator="equal" id="{5432EBEC-3A2E-4DA1-AFF4-C98E5B50DA37}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="193" operator="equal" id="{A94B1799-C1D8-45C0-BB98-00DB43B489E0}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="194" operator="equal" id="{681B80F9-3F55-49DC-B885-C33DB1D0E61F}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="195" operator="equal" id="{B6B4D882-231D-47A4-B372-D0BDA689B560}">
+            <xm:f>Metrics!$B$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="196" operator="equal" id="{CF8090E0-D7B2-4277-8C14-594891296776}">
+            <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11441,84 +11519,6 @@
               <fill>
                 <patternFill>
                   <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="191" operator="equal" id="{84D67F67-92C0-47D4-81F1-99DC3FACFD43}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFD9D9D9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="192" operator="equal" id="{5594E85F-1C39-487A-BE4C-9E152E20FBE5}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="193" operator="equal" id="{1B9E4491-B739-4D77-9543-5FA5E148239D}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="194" operator="equal" id="{AC71DD4E-2827-4827-83B6-2F24C85018D0}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="195" operator="equal" id="{D07DF7CB-968D-49A5-B5D5-A26C13402365}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="196" operator="equal" id="{7357CBBB-DA22-4DC3-A52A-DA2036E5442D}">
-            <xm:f>Metrics!$B$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11526,10 +11526,36 @@
           <xm:sqref>D19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="200" operator="equal" id="{D8FD1BDD-8230-4957-8D97-4A4847874388}">
+          <x14:cfRule type="cellIs" priority="200" operator="equal" id="{CC746B8D-203D-4122-809D-61D3B5C297F7}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
+                <color rgb="FFD9D9D9"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="201" operator="equal" id="{D390A9EF-9159-49B7-825C-517335BDCAE3}">
+            <xm:f>Metrics!$B$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="202" operator="equal" id="{10CCB798-6163-4770-B6F7-67E8DEEC3519}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
                 <color rgb="FFFFFFFF"/>
               </font>
               <fill>
@@ -11539,33 +11565,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="201" operator="equal" id="{7BD42599-EC30-496C-AC26-4EB444BDE9F5}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFD9D9D9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="202" operator="equal" id="{EDA976A1-868D-4B2C-B987-6A00934A129C}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="203" operator="equal" id="{572D64C2-CD6E-4829-8EBC-F63AF04C1D5D}">
+          <x14:cfRule type="cellIs" priority="203" operator="equal" id="{2C809529-D012-4256-901A-51A33CB49DF2}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -11578,7 +11578,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="204" operator="equal" id="{1BD08546-A5F0-40C0-BF58-A140F0301228}">
+          <x14:cfRule type="cellIs" priority="204" operator="equal" id="{6CE1E9E4-72C0-4567-B6C3-6018864592FA}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -11591,7 +11591,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="205" operator="equal" id="{859169F4-5EA1-45B7-94AB-A8593DFF4E3F}">
+          <x14:cfRule type="cellIs" priority="205" operator="equal" id="{2C4A2025-40F0-4A56-B5B7-B42BA029C040}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -11599,13 +11599,26 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="206" operator="equal" id="{4A9D4A41-5DC0-4D9B-9CA9-7F679CF58370}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor rgb="FFFFC000"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="206" operator="equal" id="{BFC782BE-9FDC-43F0-A486-F4F5138C3AAF}">
-            <xm:f>Metrics!$B$4</xm:f>
+          <x14:cfRule type="cellIs" priority="207" operator="equal" id="{7D30C214-2252-4289-B7B2-BBCA3B5AACCC}">
+            <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11613,19 +11626,6 @@
               <fill>
                 <patternFill>
                   <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="207" operator="equal" id="{2BC491D0-2789-4D60-A9C7-50D9788840D9}">
-            <xm:f>Metrics!$B$3</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11633,10 +11633,75 @@
           <xm:sqref>D17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="211" operator="equal" id="{A06D13B3-B7CD-422E-BBC1-7330474F9838}">
+          <x14:cfRule type="cellIs" priority="211" operator="equal" id="{5553DDB3-FB10-4D50-9380-40B54898A6ED}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="212" operator="equal" id="{C2D43345-FA61-4630-BF40-5DF0686AD7FC}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="213" operator="equal" id="{694E9CF6-6858-4EBA-9494-341F6989DD94}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="214" operator="equal" id="{715A2E95-B6F7-46DC-985A-EF923E92958C}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="215" operator="equal" id="{EB5720EC-57E9-4EE6-8860-67B048FDAAB9}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="216" operator="equal" id="{59B2BA67-609B-45B4-9643-12719968AF00}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
                 <color rgb="FFD9D9D9"/>
               </font>
               <fill>
@@ -11646,8 +11711,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="212" operator="equal" id="{CFC76CAD-5B9F-4F1C-8AA6-DEF444D84F7E}">
-            <xm:f>Metrics!$B$4</xm:f>
+          <x14:cfRule type="cellIs" priority="217" operator="equal" id="{649743BE-9027-4694-AF63-F5A76CD877A6}">
+            <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11659,72 +11724,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="213" operator="equal" id="{EE724A99-3D51-4252-9ADA-F67CE3FCA0AF}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="214" operator="equal" id="{4277B860-E26E-4A31-9E12-A92A4060BB6F}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="215" operator="equal" id="{DF702839-C4BD-4CDA-B15F-A85AFC993C34}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="216" operator="equal" id="{F3B98AC2-6760-4EB0-B21C-CFF3360025B3}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="217" operator="equal" id="{63BFA3AB-CDEE-4B3E-919C-659060A34F56}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="218" operator="equal" id="{B0837BC7-BE46-4623-B525-40133336A0E1}">
+          <x14:cfRule type="cellIs" priority="218" operator="equal" id="{F55A2828-C851-4F3E-B519-DA4A4E6F851A}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -11740,10 +11740,23 @@
           <xm:sqref>D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="222" operator="equal" id="{FF1B3918-AB96-4376-8780-E7FA96E937D6}">
+          <x14:cfRule type="cellIs" priority="222" operator="equal" id="{B5EBF254-D348-4EE8-86D8-7DB97B10A27B}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="223" operator="equal" id="{B0A0C0AF-A069-4F35-B494-DAC857FD6A6F}">
+            <xm:f>Metrics!$B$9</xm:f>
+            <x14:dxf>
+              <font>
                 <color rgb="FFD9D9D9"/>
               </font>
               <fill>
@@ -11753,8 +11766,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="223" operator="equal" id="{F3E5249F-9649-48D3-92E7-8BCDD7919D98}">
-            <xm:f>Metrics!$B$9</xm:f>
+          <x14:cfRule type="cellIs" priority="224" operator="equal" id="{5D9C15A1-C252-4C22-91CB-8B901538DF3C}">
+            <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11766,8 +11779,60 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="224" operator="equal" id="{D2CCCE7B-FE55-4378-B672-40ADD7907D91}">
-            <xm:f>Metrics!$B$8</xm:f>
+          <x14:cfRule type="cellIs" priority="225" operator="equal" id="{4ACAF2EF-76C4-42E0-99BC-FF144AB12C6C}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="226" operator="equal" id="{13F2ED3E-23D9-47A0-879A-DA244234E622}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="227" operator="equal" id="{F554938E-E3CE-4C6F-A07A-5724BCE72F9C}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="228" operator="equal" id="{DFC0CEDD-D41A-4AC8-9F70-4064C8E84DDE}">
+            <xm:f>Metrics!$B$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF336600"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="229" operator="equal" id="{C17D3460-A5BA-4B35-8DC1-6827AC2F2574}">
+            <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -11775,71 +11840,6 @@
               <fill>
                 <patternFill>
                   <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="225" operator="equal" id="{47F79B82-D1B9-4DB7-BC5B-273B6C231E3F}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="226" operator="equal" id="{D8B3A65D-5CF1-48F5-B618-6257DCB914A5}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="227" operator="equal" id="{FCA367B6-3FD0-4800-99D6-E079E1B828B8}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="228" operator="equal" id="{A18AF78E-431D-4F10-BB93-3B69D8404C3C}">
-            <xm:f>Metrics!$B$3</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="229" operator="equal" id="{86AEC9F5-56B6-4AF7-935F-8ED0219C3AC7}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11847,7 +11847,7 @@
           <xm:sqref>D12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="233" operator="equal" id="{E0D2B04E-DA2D-48C2-A74A-1431A056A7C8}">
+          <x14:cfRule type="cellIs" priority="233" operator="equal" id="{EE48387E-2CFA-45E5-BC3D-1728F7D3E743}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -11855,98 +11855,98 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="234" operator="equal" id="{B35183D3-F08E-421B-A5B9-6F8CBD807DBF}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="235" operator="equal" id="{1C5CC59C-92B3-4EA2-9DA9-701A66EBB074}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFD9D9D9"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="236" operator="equal" id="{ECAAC1AB-96DE-4660-8C11-5EFCBA4EB59A}">
+            <xm:f>Metrics!$B$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="237" operator="equal" id="{8AAB3B64-FBCD-4068-825A-4EF3B42667B6}">
+            <xm:f>Metrics!$B$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-0.5"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="238" operator="equal" id="{8BD0F5C6-3684-4ED5-BA51-31E6FC95B773}">
+            <xm:f>Metrics!$B$8</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="239" operator="equal" id="{23A3255D-9F4E-4871-A041-AAEF94363E96}">
+            <xm:f>Metrics!$B$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="240" operator="equal" id="{49A48430-70A4-4B97-80C4-B32621D29D24}">
+            <xm:f>Metrics!$B$10</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="234" operator="equal" id="{7FAE79A5-C4BE-4BBE-AB22-234564312143}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="235" operator="equal" id="{63E97FC0-11D1-47D7-A052-4E514026782D}">
-            <xm:f>Metrics!$B$5</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="236" operator="equal" id="{904E939D-5AEB-4F7D-9FE9-4664E7A04380}">
-            <xm:f>Metrics!$B$6</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="237" operator="equal" id="{3667E07E-8AF9-4BDF-B337-B7B020847848}">
-            <xm:f>Metrics!$B$7</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="2" tint="-0.5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="238" operator="equal" id="{12E11A4E-19BE-4F8E-BFB6-C15558B01EB0}">
-            <xm:f>Metrics!$B$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFD9D9D9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="239" operator="equal" id="{D5D05C60-BB73-4EEE-B6EF-54FD9DD03BB0}">
-            <xm:f>Metrics!$B$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="240" operator="equal" id="{90307DAC-4410-4CC0-BEA1-D057106360A0}">
-            <xm:f>Metrics!$B$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -11954,7 +11954,7 @@
           <xm:sqref>D10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="244" operator="equal" id="{7E92A482-29C6-4035-AE73-EB2E54137069}">
+          <x14:cfRule type="cellIs" priority="244" operator="equal" id="{40556AEB-622A-4A99-83E0-901C8C7FCD98}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -11962,39 +11962,52 @@
               </font>
               <fill>
                 <patternFill>
+                  <bgColor theme="0" tint="-0.35"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="245" operator="equal" id="{403E31DC-E482-4493-AD46-CF16FED0B3E8}">
+            <xm:f>Metrics!$B$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFD9D9D9"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="246" operator="equal" id="{F6273E37-9368-46A0-B4D3-345967A7F494}">
+            <xm:f>Metrics!$B$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="247" operator="equal" id="{37AE7A38-57BE-43E7-9521-C7D5DF4F1D57}">
+            <xm:f>Metrics!$B$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFFFFFF"/>
+              </font>
+              <fill>
+                <patternFill>
                   <bgColor rgb="FFC00000"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="245" operator="equal" id="{9FAA25B3-87B8-49B9-A57B-803253A0A6DE}">
-            <xm:f>Metrics!$B$3</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFD9D9D9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="246" operator="equal" id="{18502E7C-78FE-4AB0-AD7B-B77FE7DFF8BE}">
-            <xm:f>Metrics!$B$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="247" operator="equal" id="{9F3C4A72-9919-4FEB-B3AD-65BDB59AD2E7}">
-            <xm:f>Metrics!$B$5</xm:f>
+          <x14:cfRule type="cellIs" priority="248" operator="equal" id="{8060396D-23EB-418A-BCF6-8638939883E6}">
+            <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -12006,8 +12019,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="248" operator="equal" id="{156096CF-453A-42F1-A4C9-6EB8D10047B0}">
-            <xm:f>Metrics!$B$6</xm:f>
+          <x14:cfRule type="cellIs" priority="249" operator="equal" id="{FF587D2C-6CD1-4982-9CD4-66152528C457}">
+            <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -12019,8 +12032,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="249" operator="equal" id="{8FB4C3D4-76F4-46CC-9654-413C82D560B9}">
-            <xm:f>Metrics!$B$7</xm:f>
+          <x14:cfRule type="cellIs" priority="250" operator="equal" id="{5AA11398-CD61-4F45-85E7-4318B08C4174}">
+            <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -12032,8 +12045,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="250" operator="equal" id="{CB864C22-16B8-4487-AFD8-9F23C029152A}">
-            <xm:f>Metrics!$B$9</xm:f>
+          <x14:cfRule type="cellIs" priority="251" operator="equal" id="{591EC793-BAAD-4318-B71C-538E588F5460}">
+            <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FFFFFFFF"/>
@@ -12041,19 +12054,6 @@
               <fill>
                 <patternFill>
                   <bgColor rgb="FF336600"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="251" operator="equal" id="{50EE1851-F6A8-40B1-8F84-B3658F564A12}">
-            <xm:f>Metrics!$B$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.35"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -12124,7 +12124,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" s="71"/>
     </row>
@@ -12136,7 +12136,7 @@
         <v>103</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="71"/>
     </row>
@@ -12148,7 +12148,7 @@
         <v>105</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="71"/>
     </row>
@@ -12160,7 +12160,7 @@
         <v>107</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="71"/>
     </row>
@@ -12172,7 +12172,7 @@
         <v>109</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" s="71"/>
     </row>
@@ -12184,7 +12184,7 @@
         <v>111</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="71"/>
     </row>
@@ -12196,7 +12196,7 @@
         <v>113</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" s="71"/>
     </row>
@@ -12208,7 +12208,7 @@
         <v>115</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" s="71"/>
     </row>
@@ -12220,7 +12220,7 @@
         <v>117</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E12" s="71"/>
     </row>
@@ -12232,7 +12232,7 @@
         <v>119</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E13" s="71"/>
     </row>
@@ -12244,7 +12244,7 @@
         <v>121</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E14" s="71"/>
     </row>
@@ -12256,7 +12256,7 @@
         <v>123</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="71"/>
     </row>
@@ -12268,7 +12268,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E16" s="71"/>
     </row>
@@ -12280,7 +12280,7 @@
         <v>127</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" s="71"/>
     </row>
@@ -12292,7 +12292,7 @@
         <v>129</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E18" s="71"/>
     </row>
@@ -12304,7 +12304,7 @@
         <v>131</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E19" s="71"/>
     </row>
@@ -12316,7 +12316,7 @@
         <v>133</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E20" s="71"/>
     </row>
@@ -12328,7 +12328,7 @@
         <v>135</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" s="71"/>
     </row>
@@ -12340,7 +12340,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E22" s="71"/>
     </row>
@@ -12364,7 +12364,7 @@
         <v>141</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E24" s="71"/>
     </row>
@@ -12376,7 +12376,7 @@
         <v>143</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E25" s="71"/>
     </row>
@@ -12388,7 +12388,7 @@
         <v>145</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E26" s="71"/>
     </row>
@@ -12400,7 +12400,7 @@
         <v>147</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E27" s="71"/>
     </row>
@@ -12412,7 +12412,7 @@
         <v>149</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28" s="71"/>
     </row>
@@ -12424,7 +12424,7 @@
         <v>151</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E29" s="71"/>
     </row>
@@ -12436,7 +12436,7 @@
         <v>153</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E30" s="71"/>
     </row>
@@ -12448,7 +12448,7 @@
         <v>155</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E31" s="71"/>
     </row>
@@ -12460,7 +12460,7 @@
         <v>157</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E32" s="71"/>
     </row>
@@ -12472,7 +12472,7 @@
         <v>159</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E33" s="71"/>
     </row>
@@ -12484,7 +12484,7 @@
         <v>161</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E34" s="71"/>
     </row>
@@ -12496,7 +12496,7 @@
         <v>163</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E35" s="71"/>
     </row>
@@ -12508,7 +12508,7 @@
         <v>165</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E36" s="71"/>
     </row>
@@ -12520,7 +12520,7 @@
         <v>167</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E37" s="71"/>
     </row>
@@ -12532,7 +12532,7 @@
         <v>169</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E38" s="71"/>
     </row>
@@ -12544,7 +12544,7 @@
         <v>171</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E39" s="71"/>
     </row>
@@ -12556,7 +12556,7 @@
         <v>173</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E40" s="71"/>
     </row>
@@ -12578,7 +12578,7 @@
         <v>177</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E42" s="71"/>
     </row>
@@ -12590,7 +12590,7 @@
         <v>179</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E43" s="71"/>
     </row>
@@ -12602,7 +12602,7 @@
         <v>181</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E44" s="71"/>
     </row>
@@ -12614,7 +12614,7 @@
         <v>183</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E45" s="71"/>
     </row>
@@ -12626,7 +12626,7 @@
         <v>185</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E46" s="71"/>
     </row>
@@ -12638,7 +12638,7 @@
         <v>187</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E47" s="71"/>
     </row>
@@ -12650,7 +12650,7 @@
         <v>189</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E48" s="71"/>
     </row>
@@ -12662,7 +12662,7 @@
         <v>191</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E49" s="71"/>
     </row>
@@ -12684,7 +12684,7 @@
         <v>195</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E51" s="71"/>
     </row>
@@ -12696,7 +12696,7 @@
         <v>197</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E52" s="71"/>
     </row>
@@ -12708,7 +12708,7 @@
         <v>199</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E53" s="71"/>
     </row>
@@ -12720,7 +12720,7 @@
         <v>201</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E54" s="71"/>
     </row>
@@ -12732,7 +12732,7 @@
         <v>203</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E55" s="71"/>
     </row>
@@ -12744,7 +12744,7 @@
         <v>205</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E56" s="71"/>
     </row>
@@ -12756,7 +12756,7 @@
         <v>207</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E57" s="71"/>
     </row>
@@ -12768,7 +12768,7 @@
         <v>209</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E58" s="71"/>
     </row>
@@ -12780,7 +12780,7 @@
         <v>211</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E59" s="71"/>
     </row>
@@ -12792,7 +12792,7 @@
         <v>213</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E60" s="71"/>
     </row>
@@ -12804,7 +12804,7 @@
         <v>215</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E61" s="71"/>
     </row>
@@ -12816,7 +12816,7 @@
         <v>217</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E62" s="71"/>
     </row>
@@ -12828,7 +12828,7 @@
         <v>219</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E63" s="71"/>
     </row>
@@ -12840,7 +12840,7 @@
         <v>221</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E64" s="71"/>
     </row>
@@ -12862,7 +12862,7 @@
         <v>225</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -12958,7 +12958,7 @@
         <v>241</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E74" s="71"/>
     </row>
@@ -12970,7 +12970,7 @@
         <v>243</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E75" s="71"/>
     </row>
@@ -12994,7 +12994,7 @@
         <v>247</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E77" s="71"/>
     </row>
@@ -13018,7 +13018,7 @@
         <v>251</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E79" s="71"/>
     </row>
@@ -13042,7 +13042,7 @@
         <v>255</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E81" s="71"/>
     </row>
@@ -13054,7 +13054,7 @@
         <v>257</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E82" s="71"/>
     </row>
@@ -13138,7 +13138,7 @@
         <v>271</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E89" s="71"/>
     </row>
@@ -13150,7 +13150,7 @@
         <v>273</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E90" s="71"/>
     </row>
@@ -13162,7 +13162,7 @@
         <v>275</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E91" s="71"/>
     </row>
@@ -13174,7 +13174,7 @@
         <v>277</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E92" s="71"/>
     </row>
@@ -13186,7 +13186,7 @@
         <v>279</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E93" s="71"/>
     </row>
@@ -13210,7 +13210,7 @@
         <v>283</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E95" s="71"/>
     </row>
@@ -13222,7 +13222,7 @@
         <v>285</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E96" s="71"/>
     </row>
@@ -13234,7 +13234,7 @@
         <v>287</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E97" s="71"/>
     </row>
@@ -13246,7 +13246,7 @@
         <v>289</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E98" s="71"/>
     </row>
@@ -13258,7 +13258,7 @@
         <v>291</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E99" s="71"/>
     </row>
@@ -13414,7 +13414,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{8DAB9290-CD63-4BD2-80E8-D6D789AB001A}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{14DF22A0-1223-4DBC-BDA9-DC114E687060}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -13427,7 +13427,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{D085B7AD-3472-48D2-84E7-1F609C8D1010}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{9EB2006E-ED8A-4A99-AD72-15E6F1D63831}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -13440,7 +13440,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{90E96E45-BA61-4D77-ADDD-AB44797C2E91}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{105A319E-CDA9-4625-BCF4-95F927C07CB1}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -13453,7 +13453,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{171FF77C-EAF8-487C-93AB-5DE288D7E0AC}">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{F7B08171-7AE1-4885-9046-646D388528E6}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -13466,7 +13466,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{8812C137-8EE6-45BA-8BE0-403423FE6539}">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{001B6774-ADAA-4787-A884-7ABED1A8479E}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -13479,7 +13479,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{748E84B4-DD4B-4459-9AC6-BE778A3E8013}">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{16721EA5-DAD4-428C-95E0-BE760040FEAC}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -13492,7 +13492,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{A490DECE-F451-426A-A567-2590DB6F1339}">
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{41F0F89A-AAF5-4B19-B825-9671E05DD528}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -13505,7 +13505,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{1446EBAE-1289-4BE4-983E-6BB9C2688415}">
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{4B9D1A10-62E6-44D8-8CEA-5F72B560185F}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -13521,7 +13521,7 @@
           <xm:sqref>D66:D99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{A43070B2-8DB2-4380-B4EE-2BAFC66A8635}">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{4DD0C05B-5BF8-4612-9B39-707C2FFA5049}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -13534,7 +13534,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{647D5C64-805F-4DD4-81A9-5D4E7B2092C7}">
+          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{1B9878E0-3B7C-4D85-9673-42FBBA257ED7}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -13547,7 +13547,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{CD25E86C-C389-4658-B4E3-FFBC36BCFB17}">
+          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{27ED7166-57EE-4998-841A-B3815A1D7958}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -13560,7 +13560,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{25383E15-74E0-46AB-A2A4-63D29979BA19}">
+          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{626EE388-177A-4EA5-95C3-5BE42F4B1B80}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -13573,7 +13573,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{AF9E2F14-30E8-44C9-9061-BACDF0F07554}">
+          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{BE436F1E-942C-4AAC-9895-D03ABCB31F26}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -13586,7 +13586,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{3A362BDB-E017-4B24-AAF8-1517A05DEE59}">
+          <x14:cfRule type="cellIs" priority="18" operator="equal" id="{1AFB13B7-9740-4FF7-B8B3-F77070EEB550}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -13599,7 +13599,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{20D742CE-C5F8-48B2-A52B-E55FFEB576D1}">
+          <x14:cfRule type="cellIs" priority="19" operator="equal" id="{BF1B4FF9-9A8C-404E-ADBD-A123FBD0ABE0}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -13612,7 +13612,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{47A61EF0-C130-4CFE-8A80-E894DD26105D}">
+          <x14:cfRule type="cellIs" priority="20" operator="equal" id="{B4A56FE3-F6B7-4B57-9E54-6947ABE067E0}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -13628,7 +13628,7 @@
           <xm:sqref>D51:D64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{5530922A-2C66-4735-B042-8B8FCBA05B3B}">
+          <x14:cfRule type="cellIs" priority="24" operator="equal" id="{D3142F9F-11E8-4DE4-A763-00603FC041C3}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -13641,7 +13641,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{7F9D9710-60FD-4BB9-AD72-2A2916F8E430}">
+          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{30323AA9-C037-4AC0-94C7-505051D7D5FA}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -13654,7 +13654,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{E9FBA121-E1C1-4190-B7F4-D4B4E381805C}">
+          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{135649F2-5A78-4790-A077-E31A74C321EB}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -13667,7 +13667,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{F5ECFA50-E05B-4CFE-AFDD-70372021E230}">
+          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{3DF05264-BABD-4F64-85C4-EDBC4B27D33C}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -13680,7 +13680,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{B71A918C-D3AB-4DE2-B110-412C648CB96E}">
+          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{6084E0AA-537E-49CB-ABC3-BF8FF840E94D}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -13693,7 +13693,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{40F3D84E-9521-4410-A0B8-108BEBBE7839}">
+          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{B91AC36F-8C2B-4DB7-979C-AB4FC75BF318}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -13706,7 +13706,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{8B11EAE7-41FF-459B-B0E9-AC7EE271AF4A}">
+          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{E4E6AAE4-6A48-4963-8666-5FB510427ABC}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -13719,7 +13719,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{68A4C3AC-62C7-453C-9E21-D6A2FC87C130}">
+          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{E6439210-F48A-4ADD-8130-825E15527F31}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -13735,7 +13735,7 @@
           <xm:sqref>D4:D40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{DD4D8CE9-5D1F-4C1A-8959-889B30B07B73}">
+          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{39DCC627-28AE-43CE-ADF6-23799C78A410}">
             <xm:f>Metrics!$B$10</xm:f>
             <x14:dxf>
               <font>
@@ -13748,7 +13748,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{F5169757-11B1-4EE0-9817-D27C98603070}">
+          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{B8D98CFB-AA88-4B6B-91D5-493546DE18E8}">
             <xm:f>Metrics!$B$9</xm:f>
             <x14:dxf>
               <font>
@@ -13761,7 +13761,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{BF5168ED-575E-41DF-8789-7B74B656A2F6}">
+          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{6DE8AB68-4853-4670-A4BF-C4C6D52B393A}">
             <xm:f>Metrics!$B$8</xm:f>
             <x14:dxf>
               <font>
@@ -13774,7 +13774,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{48D0BE64-B147-4191-9120-D6FB9C8E6A7A}">
+          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{DB97ABF7-00D5-4F00-9F35-5CED7E4800DF}">
             <xm:f>Metrics!$B$7</xm:f>
             <x14:dxf>
               <font>
@@ -13787,7 +13787,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{8CDD524C-7571-46B4-BC85-E58461194A2F}">
+          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{58DDB5F0-3772-4531-B700-A11F8580E8E4}">
             <xm:f>Metrics!$B$6</xm:f>
             <x14:dxf>
               <font>
@@ -13800,7 +13800,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{646F2E86-EF81-4CF6-83A9-882084E14033}">
+          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{D13482AB-D1FF-4C6A-BC8E-48D953E55CBF}">
             <xm:f>Metrics!$B$5</xm:f>
             <x14:dxf>
               <font>
@@ -13813,7 +13813,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{AEF8C964-3BA2-44DB-8580-50CB2B27878B}">
+          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{36329360-26E0-455C-B936-ED19D3A31AB4}">
             <xm:f>Metrics!$B$4</xm:f>
             <x14:dxf>
               <font>
@@ -13826,7 +13826,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{56B84C36-80E8-4B6B-AE8F-F0A79070F9AC}">
+          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{85103E7C-E4D1-4FF7-BF5D-B5A6307C5475}">
             <xm:f>Metrics!$B$3</xm:f>
             <x14:dxf>
               <font>
@@ -13911,14 +13911,14 @@
     </row>
     <row r="5" s="86" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="91" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" s="92" t="s">
         <v>300</v>
       </c>
       <c r="D5" s="93" t="n">
         <f aca="false">COUNTIF('Mandatory ISMS requirements'!$D$3:$D$60,$B5)/'Mandatory ISMS requirements'!$D$61</f>
-        <v>0.25</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="E5" s="94" t="n">
         <f aca="false">COUNTIF('Annex A controls'!$D$3:$D$99,$B5)/ControlTotal</f>
@@ -13959,18 +13959,18 @@
     </row>
     <row r="8" s="86" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="91" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>305</v>
       </c>
       <c r="D8" s="93" t="n">
         <f aca="false">COUNTIF('Mandatory ISMS requirements'!$D$3:$D$60,$B8)/'Mandatory ISMS requirements'!$D$61</f>
-        <v>0.571428571428571</v>
+        <v>0.428571428571429</v>
       </c>
       <c r="E8" s="94" t="n">
         <f aca="false">COUNTIF('Annex A controls'!$D$3:$D$99,$B8)/ControlTotal</f>
-        <v>0.731182795698925</v>
+        <v>0.709677419354839</v>
       </c>
     </row>
     <row r="9" s="86" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13982,11 +13982,11 @@
       </c>
       <c r="D9" s="93" t="n">
         <f aca="false">COUNTIF('Mandatory ISMS requirements'!$D$3:$D$60,$B9)/'Mandatory ISMS requirements'!$D$61</f>
-        <v>0.178571428571429</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="E9" s="94" t="n">
         <f aca="false">COUNTIF('Annex A controls'!$D$3:$D$99,$B9)/ControlTotal</f>
-        <v>0.193548387096774</v>
+        <v>0.21505376344086</v>
       </c>
     </row>
     <row r="10" s="86" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
